--- a/Task_3/report.xlsx
+++ b/Task_3/report.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DSM Group; Фармацевтический рынок России. Май 2025</t>
+          <t>DSM Group; Фармацевтический рынок России. Май 2025 — розничный аудит фармацевтического рынка РФ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -463,12 +463,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>фармацевтический рынок; лекарственные препараты; аптечные продажи; коммерческий сегмент; локализованные препараты; импортные препараты; рецептурные препараты; безрецептурные препараты; АТС-группы; дженерики; оригинальные препараты; биологически активные добавки; производители; бренды; динамика рынка; стоимостной объём; натуральный объём</t>
+          <t>фармацевтический рынок; лекарственные препараты; розничные продажи; аптечный рынок; локализованные препараты; импортные препараты; рецептурные препараты; безрецептурные препараты; биологически активные добавки; АТС-группы; производители лекарств; дженерики; оригинальные препараты; ценовые сегменты; фармацевтическая статистика; DSM Group; ISO 9001:2015</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Отчёт DSM Group представляет анализ фармацевтического рынка России за май 2025 года. Объём коммерческого рынка лекарственных препаратов составил 146 млрд рублей, что на 15,1% больше, чем в мае 2024 года. В структуре рынка преобладают локализованные препараты (66,6% в натуральном выражении), но их доля в стоимостном выражении ниже (49,7%). Рецептурные препараты занимают 58% стоимостного объёма. Лидерами среди производителей стали Bayer, Servier и Нижфарм. В сегменте БАД объём рынка составил 13,5 млрд рублей, с лидерством бренда «Эвалар».</t>
+          <t>Отчёт DSM Group представляет анализ розничного фармацевтического рынка России за май 2025 года. Объём коммерческого рынка лекарственных препаратов составил 146 млрд рублей, что на 15,1% больше, чем в мае 2024 года. В натуральном выражении реализовано 349,2 млн упаковок, средняя стоимость упаковки — 418,2 рубля. Доля препаратов дороже 1000 рублей увеличилась до 39%, а локализованные препараты занимают 66,6% в натуральном и 49,7% в стоимостном выражении. Рецептурные препараты составляют 58% рынка в стоимостном объёме. Лидерами среди производителей стали Bayer, Servier и Нижфарм. Объём рынка БАД снизился на 5,9% до 13,5 млрд рублей. Отчет был создан не для всего файла.</t>
         </is>
       </c>
     </row>
@@ -485,12 +485,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>пациентоцентричность; система здравоохранения; ОМС; ДМС; платные медицинские услуги; диспансеризация; удовлетворенность пациентов; качество медицинской помощи; профилактическая медицина; восприятие пациентов</t>
+          <t>пациентоцентричность; система здравоохранения; ОМС; ДМС; платные медицинские услуги; диспансеризация; удовлетворенность пациентов; восприятие врача; профилактика; качество медицинской помощи</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Отчёт Центра развития здравоохранения посвящён анализу восприятия системы здравоохранения России пациентами. Исследование охватывает три ключевых сегмента: обязательное медицинское страхование (ОМС), добровольное медицинское страхование (ДМС) и платные медицинские услуги (ПМУ). Основное внимание уделяется оценке удовлетворённости пациентов, барьерам в доступе к медицинской помощи, а также пониманию принципов пациентоцентричности. В документе представлены данные количественного и качественного анализа, включая пути пациентов, совмещение сегментов здравоохранения и предложения по улучшению системы.</t>
+          <t>Отчет Центра развития здравоохранения посвящен анализу восприятия системы здравоохранения в России с точки зрения пациентов. Исследование охватывает три основных сегмента: обязательное медицинское страхование (ОМС), добровольное медицинское страхование (ДМС) и платные медицинские услуги (ПМУ). Основное внимание уделяется оценке удовлетворенности пациентов, барьерам в доступе к медицинской помощи и принципам пациентоцентричности. В документе представлены результаты количественных и качественных исследований, включая глубинные интервью и опросы среди пациентов в возрасте 35–65 лет из городов с населением свыше 500 тысяч человек. Отчет был создан не для всего файла</t>
         </is>
       </c>
     </row>
